--- a/OPECshocks_shared_Jun25.xlsx
+++ b/OPECshocks_shared_Jun25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\osiride-fs\m035315\private\Code\2024_oil\shocks_update_jun25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02FAEEB-F9A0-4D62-94A1-085CCD270229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68408DA3-DF7A-45E4-932F-2C6BFE0D463E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8595" yWindow="435" windowWidth="18900" windowHeight="12375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly" sheetId="1" r:id="rId1"/>
@@ -75,9 +75,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E504"/>
+  <dimension ref="A1:E505"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
@@ -8985,6 +8986,23 @@
       </c>
       <c r="E504">
         <v>3.7952367723497735</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A505" s="2">
+        <v>45809</v>
+      </c>
+      <c r="B505">
+        <v>0</v>
+      </c>
+      <c r="C505">
+        <v>0</v>
+      </c>
+      <c r="D505">
+        <v>0</v>
+      </c>
+      <c r="E505">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
